--- a/02_DIA_inicio_2026_analisis_assets/rbd_9593_escuela-basica-educadores-de-chile_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9593_escuela-basica-educadores-de-chile_nt2_nucleos.xlsx
@@ -727,13 +727,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A0F0F20-14C9-405B-9FED-10162D7E8A33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3290A1B-96B2-49C5-81D5-77A7C0936F66}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2A91BEB-7DA9-4E1F-AB3C-D82EDC3961AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F714440-ADF8-47F5-8F10-48081FD88079}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BF6B111-0455-45C6-A7A8-081A5422168F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7811900B-4BA8-4E05-AD9D-97EA36443A15}"/>
 </file>